--- a/file/table/DAPC_LuminariasBogota.xlsx
+++ b/file/table/DAPC_LuminariasBogota.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30508"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20797EA5-5041-4B02-A0AC-28ACF181706A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0E5741-8FD6-417F-A796-3EB03A5B4E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{85940953-CB19-47BF-B353-0BB449A22871}"/>
   </bookViews>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C22" authorId="0" shapeId="0" xr:uid="{F6D654B6-8E83-4D4C-A5C6-AE230C9FA8C2}">
+    <comment ref="C23" authorId="0" shapeId="0" xr:uid="{F6D654B6-8E83-4D4C-A5C6-AE230C9FA8C2}">
       <text>
         <r>
           <rPr>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>LED</t>
   </si>
@@ -129,9 +129,6 @@
     <t>Granja solar 1 MW</t>
   </si>
   <si>
-    <t>Generación (MWh-mes)</t>
-  </si>
-  <si>
     <t>Tipo de tecnología</t>
   </si>
   <si>
@@ -160,6 +157,12 @@
   </si>
   <si>
     <t>Costo mensual en millones de $</t>
+  </si>
+  <si>
+    <t>Consumo en MWh-hora</t>
+  </si>
+  <si>
+    <t>Generación (MWh)</t>
   </si>
 </sst>
 </file>
@@ -482,7 +485,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -568,7 +571,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -906,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319747BF-5D31-41A9-84AC-A476BC03E676}">
-  <dimension ref="B2:H24"/>
+  <dimension ref="B2:H25"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.53125" style="1" customWidth="1"/>
@@ -922,15 +928,15 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B3" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.45">
@@ -974,7 +980,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>11</v>
@@ -985,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>59016</v>
+        <v>1590.16</v>
       </c>
       <c r="D9" s="3">
         <v>40</v>
@@ -996,15 +1002,15 @@
       </c>
       <c r="F9" s="7">
         <f>C9*E9*$C$4*$C$5</f>
-        <v>566553.59999999998</v>
+        <v>15265.536000000002</v>
       </c>
       <c r="G9" s="7">
         <f>F9*$C$6/1000000</f>
-        <v>368.25984</v>
+        <v>9.9225984</v>
       </c>
       <c r="H9" s="8">
         <f>(G9/$G$12)</f>
-        <v>0.31620972684073584</v>
+        <v>0.36418466770777119</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.45">
@@ -1012,7 +1018,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="3">
-        <v>3644</v>
+        <v>1036.44</v>
       </c>
       <c r="D10" s="3">
         <v>60</v>
@@ -1023,15 +1029,15 @@
       </c>
       <c r="F10" s="7">
         <f t="shared" ref="F10:F11" si="1">C10*E10*$C$4*$C$5</f>
-        <v>52473.599999999999</v>
+        <v>14924.735999999999</v>
       </c>
       <c r="G10" s="7">
         <f t="shared" ref="G10:G11" si="2">F10*$C$6/1000000</f>
-        <v>34.107840000000003</v>
+        <v>9.7010783999999983</v>
       </c>
       <c r="H10" s="8">
         <f>(G10/$G$12)</f>
-        <v>2.9287013130531756E-2</v>
+        <v>0.35605431874689558</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.45">
@@ -1039,7 +1045,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="3">
-        <v>88839</v>
+        <v>888.39</v>
       </c>
       <c r="D11" s="3">
         <v>55</v>
@@ -1050,15 +1056,15 @@
       </c>
       <c r="F11" s="7">
         <f t="shared" si="1"/>
-        <v>1172674.8</v>
+        <v>11726.748</v>
       </c>
       <c r="G11" s="7">
         <f t="shared" si="2"/>
-        <v>762.23861999999997</v>
+        <v>7.6223862000000002</v>
       </c>
       <c r="H11" s="8">
         <f>(G11/$G$12)</f>
-        <v>0.65450326002873249</v>
+        <v>0.27976101354533317</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.45">
@@ -1067,17 +1073,17 @@
       </c>
       <c r="C12" s="14">
         <f>SUM(C9:C11)</f>
-        <v>151499</v>
+        <v>3514.9900000000002</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="15"/>
       <c r="F12" s="16">
         <f>SUM(F9:F11)</f>
-        <v>1791702</v>
+        <v>41917.020000000004</v>
       </c>
       <c r="G12" s="16">
         <f>SUM(G9:G11)</f>
-        <v>1164.6062999999999</v>
+        <v>27.246062999999999</v>
       </c>
       <c r="H12" s="17">
         <f>SUM(H9:H11)</f>
@@ -1086,105 +1092,118 @@
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="29" t="s">
-        <v>26</v>
-      </c>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="29">
         <f>F12/1000</f>
-        <v>1791.702</v>
-      </c>
+        <v>41.917020000000001</v>
+      </c>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="29">
         <f>F12/1000000</f>
-        <v>1.7917019999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="33" x14ac:dyDescent="0.45">
-      <c r="B19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="11" t="s">
+        <v>4.1917020000000006E-2</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B18" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="30">
+        <f>C16/($C$5*$C$4)</f>
+        <v>0.17465425000000001</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="20" spans="2:4" ht="33" x14ac:dyDescent="0.45">
+      <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="3">
-        <v>700</v>
-      </c>
-      <c r="D20" s="18">
-        <f>ROUNDUP($C$16/C20,0)</f>
-        <v>3</v>
+      <c r="C20" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B21" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C21" s="3">
-        <v>363</v>
+        <v>700</v>
       </c>
       <c r="D21" s="18">
-        <f>ROUNDUP($C$16/C21,0)</f>
-        <v>5</v>
+        <f>C$18/C21</f>
+        <v>2.4950607142857142E-4</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="3">
+        <v>15</v>
+      </c>
+      <c r="D22" s="18">
+        <f>C$18/C22</f>
+        <v>1.1643616666666667E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B23" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C23" s="3">
         <v>175</v>
       </c>
-      <c r="D22" s="18">
-        <f>ROUNDUP($C$16/C22,0)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B23" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="22">
+      <c r="D23" s="18">
+        <f t="shared" ref="D23:D25" si="3">C$18/C23</f>
+        <v>9.980242857142857E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B24" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="22">
         <f>8500000/12</f>
         <v>708333.33333333337</v>
       </c>
-      <c r="D23" s="18">
-        <f>$C$16/C23</f>
-        <v>2.5294616470588234E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B24" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="20">
+      <c r="D24" s="18">
+        <f t="shared" si="3"/>
+        <v>2.4657070588235293E-7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B25" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="20">
         <v>150</v>
       </c>
-      <c r="D24" s="19">
-        <f>ROUNDUP($C$16/C24,0)</f>
-        <v>12</v>
+      <c r="D25" s="19">
+        <f t="shared" si="3"/>
+        <v>1.1643616666666668E-3</v>
       </c>
     </row>
   </sheetData>
